--- a/review/adl-0.3.0-fields.xlsx
+++ b/review/adl-0.3.0-fields.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3152" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3168" uniqueCount="540">
   <si>
     <t>Field</t>
   </si>
@@ -1206,600 +1206,387 @@
     <t>Financial</t>
   </si>
   <si>
+    <t>Financial data handling configuration. REQUIRED when using this profile.</t>
+  </si>
+  <si>
     <t>financial_data_handling.pci_scope</t>
   </si>
   <si>
-    <t>PCI-DSS scope declaration</t>
+    <t>financial_data_handling.pci_scope.in_scope</t>
+  </si>
+  <si>
+    <t>financial_data_handling.pci_scope.saq_type</t>
+  </si>
+  <si>
+    <t>financial_data_handling.pci_scope.tokenization_required</t>
   </si>
   <si>
     <t>financial_data_handling.data_residency</t>
   </si>
   <si>
-    <t>array</t>
-  </si>
-  <si>
-    <t>Jurisdictional data residency requirements</t>
-  </si>
-  <si>
-    <t>financial_data_handling.pci_scope.in_scope</t>
-  </si>
-  <si>
-    <t>Whether agent operates in the cardholder data environment</t>
-  </si>
-  <si>
-    <t>financial_data_handling.pci_scope.saq_type</t>
-  </si>
-  <si>
-    <t>Self-Assessment Questionnaire type</t>
-  </si>
-  <si>
-    <t>financial_data_handling.pci_scope.tokenization_required</t>
-  </si>
-  <si>
-    <t>Whether tokenization is required for data access</t>
-  </si>
-  <si>
-    <t>financial_data_handling.data_residency.jurisdiction</t>
-  </si>
-  <si>
-    <t>ISO 3166-1 country code or region (e.g., US, EU)</t>
-  </si>
-  <si>
-    <t>financial_data_handling.data_residency.regulation</t>
-  </si>
-  <si>
-    <t>Governing regulation (e.g., GLBA, DORA, GDPR)</t>
+    <t>financial_data_handling.data_residency[].jurisdiction</t>
+  </si>
+  <si>
+    <t>financial_data_handling.data_residency[].regulation</t>
   </si>
   <si>
     <t>transaction_controls</t>
   </si>
   <si>
+    <t>Controls for agents that execute or influence financial transactions.</t>
+  </si>
+  <si>
     <t>transaction_controls.transaction_limits</t>
   </si>
   <si>
-    <t>Operational boundaries</t>
+    <t>transaction_controls.transaction_limits.max_single_amount</t>
+  </si>
+  <si>
+    <t>transaction_controls.transaction_limits.max_daily_volume</t>
+  </si>
+  <si>
+    <t>transaction_controls.transaction_limits.currency</t>
+  </si>
+  <si>
+    <t>ISO 4217 currency code</t>
   </si>
   <si>
     <t>transaction_controls.pre_execution_controls</t>
   </si>
   <si>
-    <t>Pre-trade/pre-transaction safeguards</t>
+    <t>transaction_controls.pre_execution_controls.enabled</t>
+  </si>
+  <si>
+    <t>transaction_controls.pre_execution_controls.price_tolerance_pct</t>
+  </si>
+  <si>
+    <t>transaction_controls.pre_execution_controls.throttle_per_second</t>
+  </si>
+  <si>
+    <t>transaction_controls.pre_execution_controls.requires_approval_above</t>
   </si>
   <si>
     <t>transaction_controls.kill_switch</t>
   </si>
   <si>
-    <t>Emergency stop configuration</t>
+    <t>transaction_controls.kill_switch.enabled</t>
+  </si>
+  <si>
+    <t>transaction_controls.kill_switch.trigger_conditions</t>
+  </si>
+  <si>
+    <t>transaction_controls.kill_switch.notification_targets</t>
   </si>
   <si>
     <t>transaction_controls.segregation_of_duties</t>
   </si>
   <si>
-    <t>SOX/PCI duty separation requirements</t>
-  </si>
-  <si>
-    <t>transaction_controls.transaction_limits.max_single_amount</t>
-  </si>
-  <si>
-    <t>Maximum single transaction value</t>
-  </si>
-  <si>
-    <t>transaction_controls.transaction_limits.max_daily_volume</t>
-  </si>
-  <si>
-    <t>Maximum daily aggregate volume</t>
-  </si>
-  <si>
-    <t>transaction_controls.transaction_limits.currency</t>
-  </si>
-  <si>
-    <t>ISO 4217 currency code</t>
-  </si>
-  <si>
-    <t>transaction_controls.pre_execution_controls.enabled</t>
-  </si>
-  <si>
-    <t>Whether pre-execution checks are active</t>
-  </si>
-  <si>
-    <t>transaction_controls.pre_execution_controls.price_tolerance_pct</t>
-  </si>
-  <si>
-    <t>Maximum price deviation percentage</t>
-  </si>
-  <si>
-    <t>transaction_controls.pre_execution_controls.throttle_per_second</t>
-  </si>
-  <si>
-    <t>Maximum executions per second</t>
-  </si>
-  <si>
-    <t>transaction_controls.pre_execution_controls.requires_approval_above</t>
-  </si>
-  <si>
-    <t>Amount threshold requiring human approval</t>
-  </si>
-  <si>
-    <t>transaction_controls.kill_switch.enabled</t>
-  </si>
-  <si>
-    <t>Whether kill switch is configured</t>
-  </si>
-  <si>
-    <t>transaction_controls.kill_switch.trigger_conditions</t>
-  </si>
-  <si>
-    <t>Conditions that trigger automatic halt</t>
-  </si>
-  <si>
-    <t>transaction_controls.kill_switch.notification_targets</t>
-  </si>
-  <si>
-    <t>Contacts notified on trigger</t>
-  </si>
-  <si>
     <t>transaction_controls.segregation_of_duties.enabled</t>
   </si>
   <si>
-    <t>Whether segregation is enforced</t>
-  </si>
-  <si>
     <t>transaction_controls.segregation_of_duties.restricted_actions</t>
   </si>
   <si>
-    <t>Actions that require separate authorization</t>
-  </si>
-  <si>
     <t>transaction_controls.segregation_of_duties.approval_role</t>
   </si>
   <si>
-    <t>Role that provides secondary authorization</t>
-  </si>
-  <si>
     <t>regulatory_scope</t>
   </si>
   <si>
+    <t>Declaration of which financial regulations apply to this agent.</t>
+  </si>
+  <si>
     <t>regulatory_scope.applicable_regulations</t>
   </si>
   <si>
-    <t>Financial regulations that apply</t>
+    <t>PCI_DSS_V4, SOX, GLBA, BASEL_III, FINRA, SEC_REG, DORA, MIFID_II, BSA_AML, EU_AMLD</t>
   </si>
   <si>
     <t>regulatory_scope.jurisdictions</t>
   </si>
   <si>
-    <t>Regulatory jurisdictions</t>
+    <t>regulatory_scope.jurisdictions[].jurisdiction</t>
+  </si>
+  <si>
+    <t>regulatory_scope.jurisdictions[].regulation</t>
   </si>
   <si>
     <t>regulatory_scope.reporting_obligations</t>
   </si>
   <si>
-    <t>Regulatory reporting requirements</t>
+    <t>regulatory_scope.reporting_obligations.authorities</t>
+  </si>
+  <si>
+    <t>regulatory_scope.reporting_obligations.frequency</t>
+  </si>
+  <si>
+    <t>real_time, daily, monthly, quarterly, annual</t>
   </si>
   <si>
     <t>regulatory_scope.record_retention</t>
   </si>
   <si>
-    <t>Record keeping requirements</t>
-  </si>
-  <si>
-    <t>regulatory_scope.reporting_obligations.authorities</t>
-  </si>
-  <si>
-    <t>Regulatory authorities to report to</t>
-  </si>
-  <si>
-    <t>regulatory_scope.reporting_obligations.frequency</t>
-  </si>
-  <si>
-    <t>real_time, daily, monthly, quarterly, annual</t>
-  </si>
-  <si>
-    <t>Reporting frequency: real_time, daily, monthly, quarterly, annual</t>
-  </si>
-  <si>
     <t>regulatory_scope.record_retention.min_retention_days</t>
   </si>
   <si>
-    <t>Minimum record retention in days</t>
-  </si>
-  <si>
     <t>regulatory_scope.record_retention.tamper_proof</t>
   </si>
   <si>
-    <t>Whether tamper-proof storage is required</t>
-  </si>
-  <si>
     <t>regulatory_scope.record_retention.format</t>
   </si>
   <si>
-    <t>Required record format</t>
-  </si>
-  <si>
     <t>financial_risk_management</t>
   </si>
   <si>
+    <t>Risk management controls for financial agents.</t>
+  </si>
+  <si>
     <t>financial_risk_management.model_risk</t>
   </si>
   <si>
-    <t>Model risk management (SR 11-7 / FFIEC)</t>
+    <t>financial_risk_management.model_risk.tier</t>
+  </si>
+  <si>
+    <t>tier_1, tier_2, tier_3</t>
+  </si>
+  <si>
+    <t>financial_risk_management.model_risk.validated_by</t>
+  </si>
+  <si>
+    <t>financial_risk_management.model_risk.validated_at</t>
+  </si>
+  <si>
+    <t>financial_risk_management.model_risk.methodology</t>
   </si>
   <si>
     <t>financial_risk_management.aml_controls</t>
   </si>
   <si>
-    <t>Anti-money laundering controls</t>
+    <t>financial_risk_management.aml_controls.screening_required</t>
+  </si>
+  <si>
+    <t>financial_risk_management.aml_controls.monitoring_level</t>
+  </si>
+  <si>
+    <t>real_time, daily, periodic</t>
+  </si>
+  <si>
+    <t>financial_risk_management.aml_controls.kyc_refresh_days</t>
   </si>
   <si>
     <t>financial_risk_management.operational_risk</t>
   </si>
   <si>
-    <t>Operational risk classification</t>
-  </si>
-  <si>
-    <t>financial_risk_management.model_risk.tier</t>
-  </si>
-  <si>
-    <t>tier_1, tier_2, tier_3</t>
-  </si>
-  <si>
-    <t>Model risk tier: tier_1, tier_2, tier_3</t>
-  </si>
-  <si>
-    <t>financial_risk_management.model_risk.validated_by</t>
-  </si>
-  <si>
-    <t>Validation entity</t>
-  </si>
-  <si>
-    <t>financial_risk_management.model_risk.validated_at</t>
-  </si>
-  <si>
-    <t>ISO 8601 timestamp</t>
-  </si>
-  <si>
-    <t>financial_risk_management.model_risk.methodology</t>
-  </si>
-  <si>
-    <t>Validation methodology used</t>
-  </si>
-  <si>
-    <t>financial_risk_management.aml_controls.screening_required</t>
-  </si>
-  <si>
-    <t>Whether AML screening is required</t>
-  </si>
-  <si>
-    <t>financial_risk_management.aml_controls.monitoring_level</t>
-  </si>
-  <si>
-    <t>real_time, daily, periodic</t>
-  </si>
-  <si>
-    <t>financial_risk_management.aml_controls.kyc_refresh_days</t>
-  </si>
-  <si>
-    <t>Maximum days between KYC refreshes</t>
-  </si>
-  <si>
     <t>financial_risk_management.operational_risk.category</t>
   </si>
   <si>
     <t>financial_risk_management.operational_risk.assessed_by</t>
   </si>
   <si>
-    <t>Entity that performed the assessment</t>
-  </si>
-  <si>
     <t>financial_risk_management.operational_risk.assessed_at</t>
   </si>
   <si>
     <t>financial_risk_management.operational_risk.capital_reserve</t>
   </si>
   <si>
-    <t>Whether operational risk capital is allocated</t>
+    <t>data_classification.financial</t>
   </si>
   <si>
     <t>data_classification.financial.data_types</t>
   </si>
   <si>
-    <t>Types of financial data handled</t>
+    <t>cardholder_data, sensitive_auth_data, nonpublic_personal_info, transaction_data, market_data, financial_reports, material_nonpublic_info</t>
   </si>
   <si>
     <t>data_classification.financial.pci_applicable</t>
   </si>
   <si>
-    <t>Whether PCI-DSS scope applies to this classification</t>
-  </si>
-  <si>
     <t>hipaa_compliance</t>
   </si>
   <si>
     <t>Healthcare</t>
   </si>
   <si>
+    <t>HIPAA regulatory compliance configuration. REQUIRED when using this profile.</t>
+  </si>
+  <si>
     <t>hipaa_compliance.covered_entity_type</t>
   </si>
   <si>
-    <t>Entity classification under HIPAA</t>
+    <t>covered_entity, business_associate, subcontractor</t>
   </si>
   <si>
     <t>hipaa_compliance.baa_required</t>
   </si>
   <si>
-    <t>Whether a Business Associate Agreement is required</t>
-  </si>
-  <si>
     <t>hipaa_compliance.minimum_necessary</t>
   </si>
   <si>
-    <t>Minimum necessary access configuration</t>
+    <t>hipaa_compliance.minimum_necessary.scope</t>
+  </si>
+  <si>
+    <t>task_specific, role_based, full_record</t>
+  </si>
+  <si>
+    <t>hipaa_compliance.minimum_necessary.justification</t>
+  </si>
+  <si>
+    <t>hipaa_compliance.minimum_necessary.review_frequency</t>
   </si>
   <si>
     <t>hipaa_compliance.security_rule</t>
   </si>
   <si>
-    <t>Security Rule compliance settings</t>
-  </si>
-  <si>
-    <t>hipaa_compliance.minimum_necessary.scope</t>
-  </si>
-  <si>
-    <t>Access scope level</t>
-  </si>
-  <si>
-    <t>hipaa_compliance.minimum_necessary.justification</t>
-  </si>
-  <si>
-    <t>Reason for access level</t>
-  </si>
-  <si>
-    <t>hipaa_compliance.minimum_necessary.review_frequency</t>
-  </si>
-  <si>
-    <t>How often access scope is reviewed</t>
-  </si>
-  <si>
     <t>hipaa_compliance.security_rule.encryption_at_rest</t>
   </si>
   <si>
     <t>AES_256, AES_128</t>
   </si>
   <si>
-    <t>Required algorithm: AES_256, AES_128</t>
-  </si>
-  <si>
     <t>hipaa_compliance.security_rule.encryption_in_transit</t>
   </si>
   <si>
     <t>TLS_1_2, TLS_1_3</t>
   </si>
   <si>
-    <t>Required protocol: TLS_1_2, TLS_1_3</t>
-  </si>
-  <si>
     <t>hipaa_compliance.security_rule.mfa_required</t>
   </si>
   <si>
-    <t>Whether multi-factor authentication is required</t>
-  </si>
-  <si>
     <t>hipaa_compliance.security_rule.data_retention</t>
   </si>
   <si>
     <t>none, minimum, standard</t>
   </si>
   <si>
-    <t>Retention policy: none, minimum, standard</t>
-  </si>
-  <si>
     <t>hipaa_compliance.security_rule.restoration_hours</t>
   </si>
   <si>
-    <t>Maximum hours to restore critical systems</t>
-  </si>
-  <si>
     <t>phi_handling</t>
   </si>
   <si>
+    <t>PHI data handling and de-identification controls. REQUIRED when using this profile.</t>
+  </si>
+  <si>
     <t>phi_handling.de_identification</t>
   </si>
   <si>
-    <t>De-identification method and configuration</t>
+    <t>phi_handling.de_identification.method</t>
+  </si>
+  <si>
+    <t>safe_harbor, expert_determination, none</t>
+  </si>
+  <si>
+    <t>phi_handling.de_identification.re_identification_controls</t>
   </si>
   <si>
     <t>phi_handling.breach_notification</t>
   </si>
   <si>
-    <t>Breach notification configuration</t>
+    <t>phi_handling.breach_notification.notification_hours</t>
+  </si>
+  <si>
+    <t>phi_handling.breach_notification.contact</t>
+  </si>
+  <si>
+    <t>phi_handling.breach_notification.threshold</t>
   </si>
   <si>
     <t>phi_handling.consent_management</t>
   </si>
   <si>
-    <t>Patient consent tracking</t>
+    <t>phi_handling.consent_management.required</t>
+  </si>
+  <si>
+    <t>phi_handling.consent_management.consent_types</t>
+  </si>
+  <si>
+    <t>treatment, payment, operations, research, marketing</t>
+  </si>
+  <si>
+    <t>phi_handling.consent_management.granularity</t>
+  </si>
+  <si>
+    <t>broad, purpose_specific, data_specific</t>
+  </si>
+  <si>
+    <t>phi_handling.consent_management.revocation_supported</t>
   </si>
   <si>
     <t>phi_handling.data_provenance</t>
   </si>
   <si>
-    <t>Data lineage tracking</t>
-  </si>
-  <si>
-    <t>phi_handling.de_identification.method</t>
-  </si>
-  <si>
-    <t>De-identification method</t>
-  </si>
-  <si>
-    <t>phi_handling.de_identification.re_identification_controls</t>
-  </si>
-  <si>
-    <t>Whether re-identification prevention is active</t>
-  </si>
-  <si>
-    <t>phi_handling.breach_notification.notification_hours</t>
-  </si>
-  <si>
-    <t>Maximum hours to notify authorities</t>
-  </si>
-  <si>
-    <t>phi_handling.breach_notification.contact</t>
-  </si>
-  <si>
-    <t>Breach notification contact</t>
-  </si>
-  <si>
-    <t>phi_handling.breach_notification.threshold</t>
-  </si>
-  <si>
-    <t>Number of affected individuals triggering escalated notification</t>
-  </si>
-  <si>
-    <t>phi_handling.consent_management.required</t>
-  </si>
-  <si>
-    <t>Whether explicit consent is required</t>
-  </si>
-  <si>
-    <t>phi_handling.consent_management.consent_types</t>
-  </si>
-  <si>
-    <t>treatment, payment, operations, research, marketing</t>
-  </si>
-  <si>
-    <t>Types: treatment, payment, operations, research, marketing</t>
-  </si>
-  <si>
-    <t>phi_handling.consent_management.granularity</t>
-  </si>
-  <si>
-    <t>broad, purpose_specific, data_specific</t>
-  </si>
-  <si>
-    <t>Consent granularity: broad, purpose_specific, data_specific</t>
-  </si>
-  <si>
-    <t>phi_handling.consent_management.revocation_supported</t>
-  </si>
-  <si>
-    <t>Whether consent revocation is supported</t>
-  </si>
-  <si>
     <t>phi_handling.data_provenance.tracking</t>
   </si>
   <si>
-    <t>Whether data lineage tracking is enabled</t>
-  </si>
-  <si>
     <t>phi_handling.data_provenance.source_systems</t>
   </si>
   <si>
-    <t>List of source system identifiers</t>
-  </si>
-  <si>
     <t>clinical_safety</t>
   </si>
   <si>
+    <t>Clinical safety controls for decision support or patient-facing agents.</t>
+  </si>
+  <si>
     <t>clinical_safety.fda_classification</t>
   </si>
   <si>
-    <t>FDA device/software classification</t>
+    <t>clinical_safety.fda_classification.device_class</t>
+  </si>
+  <si>
+    <t>exempt, class_I, class_II, class_III, non_device</t>
+  </si>
+  <si>
+    <t>clinical_safety.fda_classification.clearance_type</t>
+  </si>
+  <si>
+    <t>510k, de_novo, pma, not_applicable</t>
+  </si>
+  <si>
+    <t>clinical_safety.fda_classification.clearance_number</t>
+  </si>
+  <si>
+    <t>clinical_safety.fda_classification.software_level</t>
+  </si>
+  <si>
+    <t>non_significant_risk, significant_risk, life_supporting</t>
   </si>
   <si>
     <t>clinical_safety.change_control</t>
   </si>
   <si>
-    <t>Model change management (PCCP-aligned)</t>
+    <t>clinical_safety.change_control.pccp_authorized</t>
+  </si>
+  <si>
+    <t>clinical_safety.change_control.modification_scope</t>
+  </si>
+  <si>
+    <t>clinical_safety.change_control.validation_protocol</t>
+  </si>
+  <si>
+    <t>clinical_safety.change_control.rollback_plan</t>
+  </si>
+  <si>
+    <t>clinical_safety.change_control.monitoring_frequency</t>
   </si>
   <si>
     <t>clinical_safety.bias_monitoring</t>
   </si>
   <si>
-    <t>Bias detection and mitigation</t>
+    <t>clinical_safety.bias_monitoring.enabled</t>
+  </si>
+  <si>
+    <t>clinical_safety.bias_monitoring.protected_classes</t>
+  </si>
+  <si>
+    <t>clinical_safety.bias_monitoring.assessment_frequency</t>
+  </si>
+  <si>
+    <t>clinical_safety.bias_monitoring.last_assessment</t>
   </si>
   <si>
     <t>clinical_safety.human_in_the_loop</t>
   </si>
   <si>
-    <t>Clinical decision oversight</t>
-  </si>
-  <si>
-    <t>clinical_safety.fda_classification.device_class</t>
-  </si>
-  <si>
-    <t>exempt, class_I, class_II, class_III, non_device</t>
-  </si>
-  <si>
-    <t>clinical_safety.fda_classification.clearance_type</t>
-  </si>
-  <si>
-    <t>510k, de_novo, pma, not_applicable</t>
-  </si>
-  <si>
-    <t>clinical_safety.fda_classification.clearance_number</t>
-  </si>
-  <si>
-    <t>FDA clearance/approval number</t>
-  </si>
-  <si>
-    <t>clinical_safety.fda_classification.software_level</t>
-  </si>
-  <si>
-    <t>non_significant_risk, significant_risk, life_supporting</t>
-  </si>
-  <si>
-    <t>clinical_safety.change_control.pccp_authorized</t>
-  </si>
-  <si>
-    <t>Whether a PCCP has been FDA-authorized</t>
-  </si>
-  <si>
-    <t>clinical_safety.change_control.modification_scope</t>
-  </si>
-  <si>
-    <t>Authorized modification types</t>
-  </si>
-  <si>
-    <t>clinical_safety.change_control.validation_protocol</t>
-  </si>
-  <si>
-    <t>URI to validation protocol</t>
-  </si>
-  <si>
-    <t>clinical_safety.change_control.rollback_plan</t>
-  </si>
-  <si>
-    <t>Whether rollback capability exists</t>
-  </si>
-  <si>
-    <t>clinical_safety.change_control.monitoring_frequency</t>
-  </si>
-  <si>
-    <t>Real-world performance monitoring frequency</t>
-  </si>
-  <si>
-    <t>clinical_safety.bias_monitoring.enabled</t>
-  </si>
-  <si>
-    <t>Whether bias monitoring is active</t>
-  </si>
-  <si>
-    <t>clinical_safety.bias_monitoring.protected_classes</t>
-  </si>
-  <si>
-    <t>Demographics monitored for bias</t>
-  </si>
-  <si>
-    <t>clinical_safety.bias_monitoring.assessment_frequency</t>
-  </si>
-  <si>
-    <t>How often bias is assessed</t>
-  </si>
-  <si>
-    <t>clinical_safety.bias_monitoring.last_assessment</t>
-  </si>
-  <si>
     <t>clinical_safety.human_in_the_loop.level</t>
   </si>
   <si>
@@ -1809,88 +1596,58 @@
     <t>clinical_safety.human_in_the_loop.role</t>
   </si>
   <si>
-    <t>Clinical role responsible (e.g., "Physician", "Nurse Practitioner")</t>
-  </si>
-  <si>
     <t>clinical_safety.human_in_the_loop.escalation_path</t>
   </si>
   <si>
-    <t>Escalation contact or procedure</t>
-  </si>
-  <si>
     <t>interoperability</t>
   </si>
   <si>
+    <t>Health data interoperability standards compliance.</t>
+  </si>
+  <si>
     <t>interoperability.fhir_version</t>
   </si>
   <si>
-    <t>Supported FHIR version</t>
+    <t>DSTU2, STU3, R4, R4B, R5</t>
   </si>
   <si>
     <t>interoperability.terminology_bindings</t>
   </si>
   <si>
-    <t>Supported code systems</t>
-  </si>
-  <si>
     <t>interoperability.tefca_participant</t>
   </si>
   <si>
-    <t>Whether agent participates in TEFCA</t>
-  </si>
-  <si>
     <t>interoperability.information_blocking</t>
   </si>
   <si>
-    <t>21st Century Cures Act compliance</t>
+    <t>interoperability.information_blocking.compliant</t>
+  </si>
+  <si>
+    <t>interoperability.information_blocking.exceptions_claimed</t>
   </si>
   <si>
     <t>interoperability.dsi_transparency</t>
   </si>
   <si>
-    <t>ONC Decision Support Intervention transparency</t>
-  </si>
-  <si>
-    <t>interoperability.information_blocking.compliant</t>
-  </si>
-  <si>
-    <t>Whether agent is information blocking compliant</t>
-  </si>
-  <si>
-    <t>interoperability.information_blocking.exceptions_claimed</t>
-  </si>
-  <si>
-    <t>Any claimed exceptions per 45 CFR Part 171</t>
-  </si>
-  <si>
     <t>interoperability.dsi_transparency.predictive_dsi</t>
   </si>
   <si>
-    <t>Whether agent includes predictive DSI</t>
-  </si>
-  <si>
     <t>interoperability.dsi_transparency.source_attributes_published</t>
   </si>
   <si>
-    <t>Whether source attributes are disclosed</t>
-  </si>
-  <si>
     <t>interoperability.dsi_transparency.irm_practices</t>
   </si>
   <si>
-    <t>Whether Intervention Risk Management practices are documented</t>
+    <t>data_classification.healthcare</t>
   </si>
   <si>
     <t>data_classification.healthcare.phi_types</t>
   </si>
   <si>
-    <t>Categories of PHI the agent may access</t>
+    <t>demographics, medical_records, billing, mental_health, substance_use, genetic, reproductive, hiv_status</t>
   </si>
   <si>
     <t>data_classification.healthcare.hipaa_applicability</t>
-  </si>
-  <si>
-    <t>Whether HIPAA applies to this classification</t>
   </si>
 </sst>
 </file>
@@ -2335,7 +2092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H394"/>
+  <dimension ref="A1:H396"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -9543,7 +9300,7 @@
         <v>12</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>12</v>
+        <v>392</v>
       </c>
       <c r="H277" t="s">
         <v>255</v>
@@ -9551,7 +9308,7 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B278" s="11" t="s">
         <v>391</v>
@@ -9569,7 +9326,7 @@
         <v>12</v>
       </c>
       <c r="G278" s="5" t="s">
-        <v>393</v>
+        <v>12</v>
       </c>
       <c r="H278" t="s">
         <v>255</v>
@@ -9583,10 +9340,10 @@
         <v>391</v>
       </c>
       <c r="C279" t="s">
-        <v>395</v>
-      </c>
-      <c r="D279" s="6" t="s">
-        <v>25</v>
+        <v>87</v>
+      </c>
+      <c r="D279" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="E279" s="5" t="s">
         <v>12</v>
@@ -9595,7 +9352,7 @@
         <v>12</v>
       </c>
       <c r="G279" s="5" t="s">
-        <v>396</v>
+        <v>12</v>
       </c>
       <c r="H279" t="s">
         <v>255</v>
@@ -9603,16 +9360,16 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B280" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C280" t="s">
-        <v>87</v>
-      </c>
-      <c r="D280" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="D280" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E280" s="5" t="s">
         <v>12</v>
@@ -9621,7 +9378,7 @@
         <v>12</v>
       </c>
       <c r="G280" s="5" t="s">
-        <v>398</v>
+        <v>12</v>
       </c>
       <c r="H280" t="s">
         <v>255</v>
@@ -9629,13 +9386,13 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B281" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C281" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="D281" s="6" t="s">
         <v>25</v>
@@ -9647,7 +9404,7 @@
         <v>12</v>
       </c>
       <c r="G281" s="5" t="s">
-        <v>400</v>
+        <v>12</v>
       </c>
       <c r="H281" t="s">
         <v>255</v>
@@ -9655,13 +9412,13 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B282" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C282" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D282" s="6" t="s">
         <v>25</v>
@@ -9673,7 +9430,7 @@
         <v>12</v>
       </c>
       <c r="G282" s="5" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="H282" t="s">
         <v>255</v>
@@ -9681,7 +9438,7 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B283" s="11" t="s">
         <v>391</v>
@@ -9699,7 +9456,7 @@
         <v>12</v>
       </c>
       <c r="G283" s="5" t="s">
-        <v>404</v>
+        <v>12</v>
       </c>
       <c r="H283" t="s">
         <v>255</v>
@@ -9707,7 +9464,7 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B284" s="11" t="s">
         <v>391</v>
@@ -9725,7 +9482,7 @@
         <v>12</v>
       </c>
       <c r="G284" s="5" t="s">
-        <v>406</v>
+        <v>12</v>
       </c>
       <c r="H284" t="s">
         <v>255</v>
@@ -9733,7 +9490,7 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B285" s="11" t="s">
         <v>391</v>
@@ -9751,7 +9508,7 @@
         <v>12</v>
       </c>
       <c r="G285" s="5" t="s">
-        <v>12</v>
+        <v>401</v>
       </c>
       <c r="H285" t="s">
         <v>267</v>
@@ -9759,7 +9516,7 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B286" s="11" t="s">
         <v>391</v>
@@ -9777,7 +9534,7 @@
         <v>12</v>
       </c>
       <c r="G286" s="5" t="s">
-        <v>409</v>
+        <v>12</v>
       </c>
       <c r="H286" t="s">
         <v>267</v>
@@ -9785,13 +9542,13 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B287" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C287" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="D287" s="6" t="s">
         <v>25</v>
@@ -9803,7 +9560,7 @@
         <v>12</v>
       </c>
       <c r="G287" s="5" t="s">
-        <v>411</v>
+        <v>12</v>
       </c>
       <c r="H287" t="s">
         <v>267</v>
@@ -9811,13 +9568,13 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="B288" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C288" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="D288" s="6" t="s">
         <v>25</v>
@@ -9829,7 +9586,7 @@
         <v>12</v>
       </c>
       <c r="G288" s="5" t="s">
-        <v>413</v>
+        <v>12</v>
       </c>
       <c r="H288" t="s">
         <v>267</v>
@@ -9837,13 +9594,13 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="B289" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C289" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D289" s="6" t="s">
         <v>25</v>
@@ -9855,7 +9612,7 @@
         <v>12</v>
       </c>
       <c r="G289" s="5" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="H289" t="s">
         <v>267</v>
@@ -9863,16 +9620,16 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="B290" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C290" t="s">
-        <v>61</v>
-      </c>
-      <c r="D290" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D290" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E290" s="5" t="s">
         <v>12</v>
@@ -9881,7 +9638,7 @@
         <v>12</v>
       </c>
       <c r="G290" s="5" t="s">
-        <v>417</v>
+        <v>12</v>
       </c>
       <c r="H290" t="s">
         <v>267</v>
@@ -9889,16 +9646,16 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="B291" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C291" t="s">
-        <v>61</v>
-      </c>
-      <c r="D291" t="s">
-        <v>12</v>
+        <v>87</v>
+      </c>
+      <c r="D291" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E291" s="5" t="s">
         <v>12</v>
@@ -9907,7 +9664,7 @@
         <v>12</v>
       </c>
       <c r="G291" s="5" t="s">
-        <v>419</v>
+        <v>12</v>
       </c>
       <c r="H291" t="s">
         <v>267</v>
@@ -9915,16 +9672,16 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="B292" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C292" t="s">
-        <v>10</v>
-      </c>
-      <c r="D292" t="s">
-        <v>12</v>
+        <v>61</v>
+      </c>
+      <c r="D292" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E292" s="5" t="s">
         <v>12</v>
@@ -9933,7 +9690,7 @@
         <v>12</v>
       </c>
       <c r="G292" s="5" t="s">
-        <v>421</v>
+        <v>12</v>
       </c>
       <c r="H292" t="s">
         <v>267</v>
@@ -9941,16 +9698,16 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="B293" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C293" t="s">
-        <v>87</v>
-      </c>
-      <c r="D293" t="s">
-        <v>12</v>
+        <v>61</v>
+      </c>
+      <c r="D293" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E293" s="5" t="s">
         <v>12</v>
@@ -9959,7 +9716,7 @@
         <v>12</v>
       </c>
       <c r="G293" s="5" t="s">
-        <v>423</v>
+        <v>12</v>
       </c>
       <c r="H293" t="s">
         <v>267</v>
@@ -9967,7 +9724,7 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="B294" s="11" t="s">
         <v>391</v>
@@ -9975,8 +9732,8 @@
       <c r="C294" t="s">
         <v>61</v>
       </c>
-      <c r="D294" t="s">
-        <v>12</v>
+      <c r="D294" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E294" s="5" t="s">
         <v>12</v>
@@ -9985,7 +9742,7 @@
         <v>12</v>
       </c>
       <c r="G294" s="5" t="s">
-        <v>425</v>
+        <v>12</v>
       </c>
       <c r="H294" t="s">
         <v>267</v>
@@ -9993,16 +9750,16 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="B295" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C295" t="s">
-        <v>61</v>
-      </c>
-      <c r="D295" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D295" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E295" s="5" t="s">
         <v>12</v>
@@ -10011,7 +9768,7 @@
         <v>12</v>
       </c>
       <c r="G295" s="5" t="s">
-        <v>427</v>
+        <v>12</v>
       </c>
       <c r="H295" t="s">
         <v>267</v>
@@ -10019,16 +9776,16 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C296" t="s">
-        <v>61</v>
-      </c>
-      <c r="D296" t="s">
-        <v>12</v>
+        <v>87</v>
+      </c>
+      <c r="D296" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E296" s="5" t="s">
         <v>12</v>
@@ -10037,7 +9794,7 @@
         <v>12</v>
       </c>
       <c r="G296" s="5" t="s">
-        <v>429</v>
+        <v>12</v>
       </c>
       <c r="H296" t="s">
         <v>267</v>
@@ -10045,16 +9802,16 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="B297" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C297" t="s">
-        <v>87</v>
-      </c>
-      <c r="D297" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="D297" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E297" s="5" t="s">
         <v>12</v>
@@ -10063,7 +9820,7 @@
         <v>12</v>
       </c>
       <c r="G297" s="5" t="s">
-        <v>431</v>
+        <v>12</v>
       </c>
       <c r="H297" t="s">
         <v>267</v>
@@ -10071,16 +9828,16 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="B298" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C298" t="s">
-        <v>395</v>
-      </c>
-      <c r="D298" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="D298" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E298" s="5" t="s">
         <v>12</v>
@@ -10089,7 +9846,7 @@
         <v>12</v>
       </c>
       <c r="G298" s="5" t="s">
-        <v>433</v>
+        <v>12</v>
       </c>
       <c r="H298" t="s">
         <v>267</v>
@@ -10097,16 +9854,16 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="B299" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C299" t="s">
-        <v>395</v>
-      </c>
-      <c r="D299" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D299" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E299" s="5" t="s">
         <v>12</v>
@@ -10115,7 +9872,7 @@
         <v>12</v>
       </c>
       <c r="G299" s="5" t="s">
-        <v>435</v>
+        <v>12</v>
       </c>
       <c r="H299" t="s">
         <v>267</v>
@@ -10123,7 +9880,7 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="B300" s="11" t="s">
         <v>391</v>
@@ -10131,8 +9888,8 @@
       <c r="C300" t="s">
         <v>87</v>
       </c>
-      <c r="D300" t="s">
-        <v>12</v>
+      <c r="D300" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E300" s="5" t="s">
         <v>12</v>
@@ -10141,7 +9898,7 @@
         <v>12</v>
       </c>
       <c r="G300" s="5" t="s">
-        <v>437</v>
+        <v>12</v>
       </c>
       <c r="H300" t="s">
         <v>267</v>
@@ -10149,16 +9906,16 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="B301" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C301" t="s">
-        <v>395</v>
-      </c>
-      <c r="D301" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="D301" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E301" s="5" t="s">
         <v>12</v>
@@ -10167,7 +9924,7 @@
         <v>12</v>
       </c>
       <c r="G301" s="5" t="s">
-        <v>439</v>
+        <v>12</v>
       </c>
       <c r="H301" t="s">
         <v>267</v>
@@ -10175,7 +9932,7 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="B302" s="11" t="s">
         <v>391</v>
@@ -10183,8 +9940,8 @@
       <c r="C302" t="s">
         <v>10</v>
       </c>
-      <c r="D302" t="s">
-        <v>12</v>
+      <c r="D302" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E302" s="5" t="s">
         <v>12</v>
@@ -10193,7 +9950,7 @@
         <v>12</v>
       </c>
       <c r="G302" s="5" t="s">
-        <v>441</v>
+        <v>12</v>
       </c>
       <c r="H302" t="s">
         <v>267</v>
@@ -10201,7 +9958,7 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>442</v>
+        <v>420</v>
       </c>
       <c r="B303" s="11" t="s">
         <v>391</v>
@@ -10219,7 +9976,7 @@
         <v>12</v>
       </c>
       <c r="G303" s="5" t="s">
-        <v>12</v>
+        <v>421</v>
       </c>
       <c r="H303" t="s">
         <v>274</v>
@@ -10227,25 +9984,25 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="B304" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C304" t="s">
-        <v>395</v>
-      </c>
-      <c r="D304" s="8" t="s">
-        <v>283</v>
+        <v>64</v>
+      </c>
+      <c r="D304" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="E304" s="5" t="s">
-        <v>12</v>
+        <v>423</v>
       </c>
       <c r="F304" t="s">
         <v>12</v>
       </c>
       <c r="G304" s="5" t="s">
-        <v>444</v>
+        <v>12</v>
       </c>
       <c r="H304" t="s">
         <v>274</v>
@@ -10253,13 +10010,13 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>445</v>
+        <v>424</v>
       </c>
       <c r="B305" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C305" t="s">
-        <v>395</v>
+        <v>71</v>
       </c>
       <c r="D305" s="6" t="s">
         <v>25</v>
@@ -10271,7 +10028,7 @@
         <v>12</v>
       </c>
       <c r="G305" s="5" t="s">
-        <v>446</v>
+        <v>12</v>
       </c>
       <c r="H305" t="s">
         <v>274</v>
@@ -10279,13 +10036,13 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="B306" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C306" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D306" s="6" t="s">
         <v>25</v>
@@ -10297,7 +10054,7 @@
         <v>12</v>
       </c>
       <c r="G306" s="5" t="s">
-        <v>448</v>
+        <v>12</v>
       </c>
       <c r="H306" t="s">
         <v>274</v>
@@ -10305,13 +10062,13 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="B307" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C307" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D307" s="6" t="s">
         <v>25</v>
@@ -10323,7 +10080,7 @@
         <v>12</v>
       </c>
       <c r="G307" s="5" t="s">
-        <v>450</v>
+        <v>12</v>
       </c>
       <c r="H307" t="s">
         <v>274</v>
@@ -10331,16 +10088,16 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="B308" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C308" t="s">
-        <v>395</v>
-      </c>
-      <c r="D308" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D308" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E308" s="5" t="s">
         <v>12</v>
@@ -10349,7 +10106,7 @@
         <v>12</v>
       </c>
       <c r="G308" s="5" t="s">
-        <v>452</v>
+        <v>12</v>
       </c>
       <c r="H308" t="s">
         <v>274</v>
@@ -10357,25 +10114,25 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="B309" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C309" t="s">
-        <v>10</v>
-      </c>
-      <c r="D309" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="D309" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E309" s="5" t="s">
-        <v>454</v>
+        <v>12</v>
       </c>
       <c r="F309" t="s">
         <v>12</v>
       </c>
       <c r="G309" s="5" t="s">
-        <v>455</v>
+        <v>12</v>
       </c>
       <c r="H309" t="s">
         <v>274</v>
@@ -10383,25 +10140,25 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="B310" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C310" t="s">
-        <v>61</v>
-      </c>
-      <c r="D310" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="D310" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E310" s="5" t="s">
-        <v>12</v>
+        <v>430</v>
       </c>
       <c r="F310" t="s">
         <v>12</v>
       </c>
       <c r="G310" s="5" t="s">
-        <v>457</v>
+        <v>12</v>
       </c>
       <c r="H310" t="s">
         <v>274</v>
@@ -10409,16 +10166,16 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="B311" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C311" t="s">
-        <v>87</v>
-      </c>
-      <c r="D311" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D311" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E311" s="5" t="s">
         <v>12</v>
@@ -10427,7 +10184,7 @@
         <v>12</v>
       </c>
       <c r="G311" s="5" t="s">
-        <v>459</v>
+        <v>12</v>
       </c>
       <c r="H311" t="s">
         <v>274</v>
@@ -10435,16 +10192,16 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>460</v>
+        <v>432</v>
       </c>
       <c r="B312" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C312" t="s">
-        <v>10</v>
-      </c>
-      <c r="D312" t="s">
-        <v>12</v>
+        <v>61</v>
+      </c>
+      <c r="D312" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E312" s="5" t="s">
         <v>12</v>
@@ -10453,7 +10210,7 @@
         <v>12</v>
       </c>
       <c r="G312" s="5" t="s">
-        <v>461</v>
+        <v>12</v>
       </c>
       <c r="H312" t="s">
         <v>274</v>
@@ -10461,13 +10218,13 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>462</v>
+        <v>433</v>
       </c>
       <c r="B313" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C313" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="D313" s="6" t="s">
         <v>25</v>
@@ -10482,18 +10239,18 @@
         <v>12</v>
       </c>
       <c r="H313" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>463</v>
+        <v>434</v>
       </c>
       <c r="B314" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C314" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D314" s="6" t="s">
         <v>25</v>
@@ -10505,15 +10262,15 @@
         <v>12</v>
       </c>
       <c r="G314" s="5" t="s">
-        <v>464</v>
+        <v>12</v>
       </c>
       <c r="H314" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>465</v>
+        <v>435</v>
       </c>
       <c r="B315" s="11" t="s">
         <v>391</v>
@@ -10531,7 +10288,7 @@
         <v>12</v>
       </c>
       <c r="G315" s="5" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="H315" t="s">
         <v>284</v>
@@ -10539,7 +10296,7 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>467</v>
+        <v>437</v>
       </c>
       <c r="B316" s="11" t="s">
         <v>391</v>
@@ -10557,7 +10314,7 @@
         <v>12</v>
       </c>
       <c r="G316" s="5" t="s">
-        <v>468</v>
+        <v>12</v>
       </c>
       <c r="H316" t="s">
         <v>284</v>
@@ -10565,7 +10322,7 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>469</v>
+        <v>438</v>
       </c>
       <c r="B317" s="11" t="s">
         <v>391</v>
@@ -10573,17 +10330,17 @@
       <c r="C317" t="s">
         <v>10</v>
       </c>
-      <c r="D317" t="s">
-        <v>12</v>
+      <c r="D317" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E317" s="5" t="s">
-        <v>470</v>
+        <v>439</v>
       </c>
       <c r="F317" t="s">
         <v>12</v>
       </c>
       <c r="G317" s="5" t="s">
-        <v>471</v>
+        <v>12</v>
       </c>
       <c r="H317" t="s">
         <v>284</v>
@@ -10591,7 +10348,7 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>472</v>
+        <v>440</v>
       </c>
       <c r="B318" s="11" t="s">
         <v>391</v>
@@ -10599,8 +10356,8 @@
       <c r="C318" t="s">
         <v>10</v>
       </c>
-      <c r="D318" t="s">
-        <v>12</v>
+      <c r="D318" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E318" s="5" t="s">
         <v>12</v>
@@ -10609,7 +10366,7 @@
         <v>12</v>
       </c>
       <c r="G318" s="5" t="s">
-        <v>473</v>
+        <v>12</v>
       </c>
       <c r="H318" t="s">
         <v>284</v>
@@ -10617,7 +10374,7 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="B319" s="11" t="s">
         <v>391</v>
@@ -10625,8 +10382,8 @@
       <c r="C319" t="s">
         <v>10</v>
       </c>
-      <c r="D319" t="s">
-        <v>12</v>
+      <c r="D319" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E319" s="5" t="s">
         <v>12</v>
@@ -10635,7 +10392,7 @@
         <v>12</v>
       </c>
       <c r="G319" s="5" t="s">
-        <v>475</v>
+        <v>12</v>
       </c>
       <c r="H319" t="s">
         <v>284</v>
@@ -10643,7 +10400,7 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>476</v>
+        <v>442</v>
       </c>
       <c r="B320" s="11" t="s">
         <v>391</v>
@@ -10651,8 +10408,8 @@
       <c r="C320" t="s">
         <v>10</v>
       </c>
-      <c r="D320" t="s">
-        <v>12</v>
+      <c r="D320" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E320" s="5" t="s">
         <v>12</v>
@@ -10661,7 +10418,7 @@
         <v>12</v>
       </c>
       <c r="G320" s="5" t="s">
-        <v>477</v>
+        <v>12</v>
       </c>
       <c r="H320" t="s">
         <v>284</v>
@@ -10669,16 +10426,16 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="B321" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C321" t="s">
-        <v>87</v>
-      </c>
-      <c r="D321" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D321" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E321" s="5" t="s">
         <v>12</v>
@@ -10687,7 +10444,7 @@
         <v>12</v>
       </c>
       <c r="G321" s="5" t="s">
-        <v>479</v>
+        <v>12</v>
       </c>
       <c r="H321" t="s">
         <v>284</v>
@@ -10695,25 +10452,25 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>480</v>
+        <v>444</v>
       </c>
       <c r="B322" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C322" t="s">
-        <v>10</v>
-      </c>
-      <c r="D322" t="s">
-        <v>12</v>
+        <v>87</v>
+      </c>
+      <c r="D322" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E322" s="5" t="s">
-        <v>481</v>
+        <v>12</v>
       </c>
       <c r="F322" t="s">
         <v>12</v>
       </c>
       <c r="G322" s="5" t="s">
-        <v>481</v>
+        <v>12</v>
       </c>
       <c r="H322" t="s">
         <v>284</v>
@@ -10721,25 +10478,25 @@
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
       <c r="B323" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C323" t="s">
-        <v>61</v>
-      </c>
-      <c r="D323" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="D323" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E323" s="5" t="s">
-        <v>12</v>
+        <v>446</v>
       </c>
       <c r="F323" t="s">
         <v>12</v>
       </c>
       <c r="G323" s="5" t="s">
-        <v>483</v>
+        <v>12</v>
       </c>
       <c r="H323" t="s">
         <v>284</v>
@@ -10747,25 +10504,25 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>484</v>
+        <v>447</v>
       </c>
       <c r="B324" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C324" t="s">
-        <v>10</v>
-      </c>
-      <c r="D324" t="s">
-        <v>12</v>
+        <v>61</v>
+      </c>
+      <c r="D324" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E324" s="5" t="s">
-        <v>276</v>
+        <v>12</v>
       </c>
       <c r="F324" t="s">
         <v>12</v>
       </c>
       <c r="G324" s="5" t="s">
-        <v>276</v>
+        <v>12</v>
       </c>
       <c r="H324" t="s">
         <v>284</v>
@@ -10773,16 +10530,16 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="B325" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C325" t="s">
-        <v>10</v>
-      </c>
-      <c r="D325" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D325" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E325" s="5" t="s">
         <v>12</v>
@@ -10791,7 +10548,7 @@
         <v>12</v>
       </c>
       <c r="G325" s="5" t="s">
-        <v>486</v>
+        <v>12</v>
       </c>
       <c r="H325" t="s">
         <v>284</v>
@@ -10799,7 +10556,7 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>487</v>
+        <v>449</v>
       </c>
       <c r="B326" s="11" t="s">
         <v>391</v>
@@ -10807,17 +10564,17 @@
       <c r="C326" t="s">
         <v>10</v>
       </c>
-      <c r="D326" t="s">
-        <v>12</v>
+      <c r="D326" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E326" s="5" t="s">
-        <v>12</v>
+        <v>276</v>
       </c>
       <c r="F326" t="s">
         <v>12</v>
       </c>
       <c r="G326" s="5" t="s">
-        <v>475</v>
+        <v>12</v>
       </c>
       <c r="H326" t="s">
         <v>284</v>
@@ -10825,16 +10582,16 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>488</v>
+        <v>450</v>
       </c>
       <c r="B327" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C327" t="s">
-        <v>87</v>
-      </c>
-      <c r="D327" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="D327" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E327" s="5" t="s">
         <v>12</v>
@@ -10843,7 +10600,7 @@
         <v>12</v>
       </c>
       <c r="G327" s="5" t="s">
-        <v>489</v>
+        <v>12</v>
       </c>
       <c r="H327" t="s">
         <v>284</v>
@@ -10851,16 +10608,16 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>195</v>
+        <v>451</v>
       </c>
       <c r="B328" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C328" t="s">
-        <v>24</v>
-      </c>
-      <c r="D328" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="D328" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E328" s="5" t="s">
         <v>12</v>
@@ -10872,21 +10629,21 @@
         <v>12</v>
       </c>
       <c r="H328" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>490</v>
+        <v>452</v>
       </c>
       <c r="B329" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C329" t="s">
-        <v>395</v>
-      </c>
-      <c r="D329" s="4" t="s">
-        <v>11</v>
+        <v>87</v>
+      </c>
+      <c r="D329" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E329" s="5" t="s">
         <v>12</v>
@@ -10895,24 +10652,24 @@
         <v>12</v>
       </c>
       <c r="G329" s="5" t="s">
-        <v>491</v>
+        <v>12</v>
       </c>
       <c r="H329" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>492</v>
+        <v>453</v>
       </c>
       <c r="B330" s="11" t="s">
         <v>391</v>
       </c>
       <c r="C330" t="s">
-        <v>87</v>
-      </c>
-      <c r="D330" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="D330" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="E330" s="5" t="s">
         <v>12</v>
@@ -10921,7 +10678,7 @@
         <v>12</v>
       </c>
       <c r="G330" s="5" t="s">
-        <v>493</v>
+        <v>12</v>
       </c>
       <c r="H330" t="s">
         <v>294</v>
@@ -10929,19 +10686,19 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="B331" s="12" t="s">
-        <v>495</v>
+        <v>454</v>
+      </c>
+      <c r="B331" s="11" t="s">
+        <v>391</v>
       </c>
       <c r="C331" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E331" s="5" t="s">
-        <v>12</v>
+        <v>455</v>
       </c>
       <c r="F331" t="s">
         <v>12</v>
@@ -10950,21 +10707,21 @@
         <v>12</v>
       </c>
       <c r="H331" t="s">
-        <v>255</v>
+        <v>294</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="B332" s="12" t="s">
-        <v>495</v>
+        <v>456</v>
+      </c>
+      <c r="B332" s="11" t="s">
+        <v>391</v>
       </c>
       <c r="C332" t="s">
-        <v>10</v>
-      </c>
-      <c r="D332" s="4" t="s">
-        <v>11</v>
+        <v>87</v>
+      </c>
+      <c r="D332" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E332" s="5" t="s">
         <v>12</v>
@@ -10973,21 +10730,21 @@
         <v>12</v>
       </c>
       <c r="G332" s="5" t="s">
-        <v>497</v>
+        <v>12</v>
       </c>
       <c r="H332" t="s">
-        <v>255</v>
+        <v>294</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>498</v>
+        <v>457</v>
       </c>
       <c r="B333" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C333" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>11</v>
@@ -10999,7 +10756,7 @@
         <v>12</v>
       </c>
       <c r="G333" s="5" t="s">
-        <v>499</v>
+        <v>459</v>
       </c>
       <c r="H333" t="s">
         <v>255</v>
@@ -11007,25 +10764,25 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="B334" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C334" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E334" s="5" t="s">
-        <v>12</v>
+        <v>461</v>
       </c>
       <c r="F334" t="s">
         <v>12</v>
       </c>
       <c r="G334" s="5" t="s">
-        <v>501</v>
+        <v>12</v>
       </c>
       <c r="H334" t="s">
         <v>255</v>
@@ -11033,16 +10790,16 @@
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="B335" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C335" t="s">
-        <v>24</v>
-      </c>
-      <c r="D335" s="6" t="s">
-        <v>25</v>
+        <v>87</v>
+      </c>
+      <c r="D335" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="E335" s="5" t="s">
         <v>12</v>
@@ -11051,7 +10808,7 @@
         <v>12</v>
       </c>
       <c r="G335" s="5" t="s">
-        <v>503</v>
+        <v>12</v>
       </c>
       <c r="H335" t="s">
         <v>255</v>
@@ -11059,13 +10816,13 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>504</v>
+        <v>463</v>
       </c>
       <c r="B336" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C336" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>11</v>
@@ -11077,7 +10834,7 @@
         <v>12</v>
       </c>
       <c r="G336" s="5" t="s">
-        <v>505</v>
+        <v>12</v>
       </c>
       <c r="H336" t="s">
         <v>255</v>
@@ -11085,25 +10842,25 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>506</v>
+        <v>464</v>
       </c>
       <c r="B337" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C337" t="s">
         <v>10</v>
       </c>
-      <c r="D337" s="6" t="s">
-        <v>25</v>
+      <c r="D337" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="E337" s="5" t="s">
-        <v>12</v>
+        <v>465</v>
       </c>
       <c r="F337" t="s">
         <v>12</v>
       </c>
       <c r="G337" s="5" t="s">
-        <v>507</v>
+        <v>12</v>
       </c>
       <c r="H337" t="s">
         <v>255</v>
@@ -11111,10 +10868,10 @@
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>508</v>
+        <v>466</v>
       </c>
       <c r="B338" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C338" t="s">
         <v>10</v>
@@ -11129,7 +10886,7 @@
         <v>12</v>
       </c>
       <c r="G338" s="5" t="s">
-        <v>509</v>
+        <v>12</v>
       </c>
       <c r="H338" t="s">
         <v>255</v>
@@ -11137,25 +10894,25 @@
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>510</v>
+        <v>467</v>
       </c>
       <c r="B339" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C339" t="s">
         <v>10</v>
       </c>
-      <c r="D339" t="s">
-        <v>12</v>
+      <c r="D339" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E339" s="5" t="s">
-        <v>511</v>
+        <v>12</v>
       </c>
       <c r="F339" t="s">
         <v>12</v>
       </c>
       <c r="G339" s="5" t="s">
-        <v>512</v>
+        <v>12</v>
       </c>
       <c r="H339" t="s">
         <v>255</v>
@@ -11163,25 +10920,25 @@
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>513</v>
+        <v>468</v>
       </c>
       <c r="B340" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C340" t="s">
-        <v>10</v>
-      </c>
-      <c r="D340" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D340" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E340" s="5" t="s">
-        <v>514</v>
+        <v>12</v>
       </c>
       <c r="F340" t="s">
         <v>12</v>
       </c>
       <c r="G340" s="5" t="s">
-        <v>515</v>
+        <v>12</v>
       </c>
       <c r="H340" t="s">
         <v>255</v>
@@ -11189,25 +10946,25 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>516</v>
+        <v>469</v>
       </c>
       <c r="B341" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C341" t="s">
-        <v>87</v>
-      </c>
-      <c r="D341" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="D341" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E341" s="5" t="s">
-        <v>12</v>
+        <v>470</v>
       </c>
       <c r="F341" t="s">
         <v>12</v>
       </c>
       <c r="G341" s="5" t="s">
-        <v>517</v>
+        <v>12</v>
       </c>
       <c r="H341" t="s">
         <v>255</v>
@@ -11215,25 +10972,25 @@
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>518</v>
+        <v>471</v>
       </c>
       <c r="B342" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C342" t="s">
         <v>10</v>
       </c>
-      <c r="D342" t="s">
-        <v>12</v>
+      <c r="D342" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E342" s="5" t="s">
-        <v>519</v>
+        <v>472</v>
       </c>
       <c r="F342" t="s">
         <v>12</v>
       </c>
       <c r="G342" s="5" t="s">
-        <v>520</v>
+        <v>12</v>
       </c>
       <c r="H342" t="s">
         <v>255</v>
@@ -11241,16 +10998,16 @@
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>521</v>
+        <v>473</v>
       </c>
       <c r="B343" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C343" t="s">
-        <v>61</v>
-      </c>
-      <c r="D343" t="s">
-        <v>12</v>
+        <v>87</v>
+      </c>
+      <c r="D343" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E343" s="5" t="s">
         <v>12</v>
@@ -11259,7 +11016,7 @@
         <v>12</v>
       </c>
       <c r="G343" s="5" t="s">
-        <v>522</v>
+        <v>12</v>
       </c>
       <c r="H343" t="s">
         <v>255</v>
@@ -11267,19 +11024,19 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>523</v>
+        <v>474</v>
       </c>
       <c r="B344" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C344" t="s">
-        <v>24</v>
-      </c>
-      <c r="D344" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="D344" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E344" s="5" t="s">
-        <v>12</v>
+        <v>475</v>
       </c>
       <c r="F344" t="s">
         <v>12</v>
@@ -11288,21 +11045,21 @@
         <v>12</v>
       </c>
       <c r="H344" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>524</v>
+        <v>476</v>
       </c>
       <c r="B345" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C345" t="s">
-        <v>24</v>
-      </c>
-      <c r="D345" s="4" t="s">
-        <v>11</v>
+        <v>61</v>
+      </c>
+      <c r="D345" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E345" s="5" t="s">
         <v>12</v>
@@ -11311,18 +11068,18 @@
         <v>12</v>
       </c>
       <c r="G345" s="5" t="s">
-        <v>525</v>
+        <v>12</v>
       </c>
       <c r="H345" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>526</v>
+        <v>477</v>
       </c>
       <c r="B346" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C346" t="s">
         <v>24</v>
@@ -11337,7 +11094,7 @@
         <v>12</v>
       </c>
       <c r="G346" s="5" t="s">
-        <v>527</v>
+        <v>478</v>
       </c>
       <c r="H346" t="s">
         <v>267</v>
@@ -11345,16 +11102,16 @@
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>528</v>
+        <v>479</v>
       </c>
       <c r="B347" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C347" t="s">
         <v>24</v>
       </c>
-      <c r="D347" s="6" t="s">
-        <v>25</v>
+      <c r="D347" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="E347" s="5" t="s">
         <v>12</v>
@@ -11363,7 +11120,7 @@
         <v>12</v>
       </c>
       <c r="G347" s="5" t="s">
-        <v>529</v>
+        <v>12</v>
       </c>
       <c r="H347" t="s">
         <v>267</v>
@@ -11371,25 +11128,25 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>530</v>
+        <v>480</v>
       </c>
       <c r="B348" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C348" t="s">
-        <v>24</v>
-      </c>
-      <c r="D348" s="6" t="s">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="D348" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="E348" s="5" t="s">
-        <v>12</v>
+        <v>481</v>
       </c>
       <c r="F348" t="s">
         <v>12</v>
       </c>
       <c r="G348" s="5" t="s">
-        <v>531</v>
+        <v>12</v>
       </c>
       <c r="H348" t="s">
         <v>267</v>
@@ -11397,16 +11154,16 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>532</v>
+        <v>482</v>
       </c>
       <c r="B349" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C349" t="s">
-        <v>10</v>
-      </c>
-      <c r="D349" s="4" t="s">
-        <v>11</v>
+        <v>87</v>
+      </c>
+      <c r="D349" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E349" s="5" t="s">
         <v>12</v>
@@ -11415,7 +11172,7 @@
         <v>12</v>
       </c>
       <c r="G349" s="5" t="s">
-        <v>533</v>
+        <v>12</v>
       </c>
       <c r="H349" t="s">
         <v>267</v>
@@ -11423,16 +11180,16 @@
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>534</v>
+        <v>483</v>
       </c>
       <c r="B350" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C350" t="s">
-        <v>87</v>
-      </c>
-      <c r="D350" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="D350" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="E350" s="5" t="s">
         <v>12</v>
@@ -11441,7 +11198,7 @@
         <v>12</v>
       </c>
       <c r="G350" s="5" t="s">
-        <v>535</v>
+        <v>12</v>
       </c>
       <c r="H350" t="s">
         <v>267</v>
@@ -11449,10 +11206,10 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>536</v>
+        <v>484</v>
       </c>
       <c r="B351" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C351" t="s">
         <v>61</v>
@@ -11467,7 +11224,7 @@
         <v>12</v>
       </c>
       <c r="G351" s="5" t="s">
-        <v>537</v>
+        <v>12</v>
       </c>
       <c r="H351" t="s">
         <v>267</v>
@@ -11475,10 +11232,10 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>538</v>
+        <v>485</v>
       </c>
       <c r="B352" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C352" t="s">
         <v>10</v>
@@ -11493,7 +11250,7 @@
         <v>12</v>
       </c>
       <c r="G352" s="5" t="s">
-        <v>539</v>
+        <v>12</v>
       </c>
       <c r="H352" t="s">
         <v>267</v>
@@ -11501,10 +11258,10 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>540</v>
+        <v>486</v>
       </c>
       <c r="B353" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C353" t="s">
         <v>61</v>
@@ -11519,7 +11276,7 @@
         <v>12</v>
       </c>
       <c r="G353" s="5" t="s">
-        <v>541</v>
+        <v>12</v>
       </c>
       <c r="H353" t="s">
         <v>267</v>
@@ -11527,16 +11284,16 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>542</v>
+        <v>487</v>
       </c>
       <c r="B354" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C354" t="s">
-        <v>87</v>
-      </c>
-      <c r="D354" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D354" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E354" s="5" t="s">
         <v>12</v>
@@ -11545,7 +11302,7 @@
         <v>12</v>
       </c>
       <c r="G354" s="5" t="s">
-        <v>543</v>
+        <v>12</v>
       </c>
       <c r="H354" t="s">
         <v>267</v>
@@ -11553,25 +11310,25 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>544</v>
+        <v>488</v>
       </c>
       <c r="B355" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C355" t="s">
-        <v>395</v>
-      </c>
-      <c r="D355" t="s">
-        <v>12</v>
+        <v>87</v>
+      </c>
+      <c r="D355" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E355" s="5" t="s">
-        <v>545</v>
+        <v>12</v>
       </c>
       <c r="F355" t="s">
         <v>12</v>
       </c>
       <c r="G355" s="5" t="s">
-        <v>546</v>
+        <v>12</v>
       </c>
       <c r="H355" t="s">
         <v>267</v>
@@ -11579,25 +11336,25 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>547</v>
+        <v>489</v>
       </c>
       <c r="B356" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C356" t="s">
-        <v>10</v>
-      </c>
-      <c r="D356" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="D356" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E356" s="5" t="s">
-        <v>548</v>
+        <v>490</v>
       </c>
       <c r="F356" t="s">
         <v>12</v>
       </c>
       <c r="G356" s="5" t="s">
-        <v>549</v>
+        <v>12</v>
       </c>
       <c r="H356" t="s">
         <v>267</v>
@@ -11605,25 +11362,25 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>550</v>
+        <v>491</v>
       </c>
       <c r="B357" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C357" t="s">
-        <v>87</v>
-      </c>
-      <c r="D357" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="D357" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E357" s="5" t="s">
-        <v>12</v>
+        <v>492</v>
       </c>
       <c r="F357" t="s">
         <v>12</v>
       </c>
       <c r="G357" s="5" t="s">
-        <v>551</v>
+        <v>12</v>
       </c>
       <c r="H357" t="s">
         <v>267</v>
@@ -11631,16 +11388,16 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>552</v>
+        <v>493</v>
       </c>
       <c r="B358" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C358" t="s">
         <v>87</v>
       </c>
-      <c r="D358" t="s">
-        <v>12</v>
+      <c r="D358" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E358" s="5" t="s">
         <v>12</v>
@@ -11649,7 +11406,7 @@
         <v>12</v>
       </c>
       <c r="G358" s="5" t="s">
-        <v>553</v>
+        <v>12</v>
       </c>
       <c r="H358" t="s">
         <v>267</v>
@@ -11657,16 +11414,16 @@
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>554</v>
+        <v>494</v>
       </c>
       <c r="B359" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C359" t="s">
-        <v>395</v>
-      </c>
-      <c r="D359" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D359" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E359" s="5" t="s">
         <v>12</v>
@@ -11675,7 +11432,7 @@
         <v>12</v>
       </c>
       <c r="G359" s="5" t="s">
-        <v>555</v>
+        <v>12</v>
       </c>
       <c r="H359" t="s">
         <v>267</v>
@@ -11683,13 +11440,13 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>556</v>
+        <v>495</v>
       </c>
       <c r="B360" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C360" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="D360" s="6" t="s">
         <v>25</v>
@@ -11704,18 +11461,18 @@
         <v>12</v>
       </c>
       <c r="H360" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>557</v>
+        <v>496</v>
       </c>
       <c r="B361" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C361" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D361" s="6" t="s">
         <v>25</v>
@@ -11727,18 +11484,18 @@
         <v>12</v>
       </c>
       <c r="G361" s="5" t="s">
-        <v>558</v>
+        <v>12</v>
       </c>
       <c r="H361" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>559</v>
+        <v>497</v>
       </c>
       <c r="B362" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C362" t="s">
         <v>24</v>
@@ -11753,7 +11510,7 @@
         <v>12</v>
       </c>
       <c r="G362" s="5" t="s">
-        <v>560</v>
+        <v>498</v>
       </c>
       <c r="H362" t="s">
         <v>274</v>
@@ -11761,10 +11518,10 @@
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>561</v>
+        <v>499</v>
       </c>
       <c r="B363" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C363" t="s">
         <v>24</v>
@@ -11779,7 +11536,7 @@
         <v>12</v>
       </c>
       <c r="G363" s="5" t="s">
-        <v>562</v>
+        <v>12</v>
       </c>
       <c r="H363" t="s">
         <v>274</v>
@@ -11787,25 +11544,25 @@
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>563</v>
+        <v>500</v>
       </c>
       <c r="B364" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C364" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D364" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E364" s="5" t="s">
-        <v>12</v>
+        <v>501</v>
       </c>
       <c r="F364" t="s">
         <v>12</v>
       </c>
       <c r="G364" s="5" t="s">
-        <v>564</v>
+        <v>12</v>
       </c>
       <c r="H364" t="s">
         <v>274</v>
@@ -11813,25 +11570,25 @@
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>565</v>
+        <v>502</v>
       </c>
       <c r="B365" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C365" t="s">
         <v>10</v>
       </c>
-      <c r="D365" t="s">
-        <v>12</v>
+      <c r="D365" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E365" s="5" t="s">
-        <v>566</v>
+        <v>503</v>
       </c>
       <c r="F365" t="s">
         <v>12</v>
       </c>
       <c r="G365" s="5" t="s">
-        <v>566</v>
+        <v>12</v>
       </c>
       <c r="H365" t="s">
         <v>274</v>
@@ -11839,25 +11596,25 @@
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>567</v>
+        <v>504</v>
       </c>
       <c r="B366" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C366" t="s">
         <v>10</v>
       </c>
-      <c r="D366" t="s">
-        <v>12</v>
+      <c r="D366" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E366" s="5" t="s">
-        <v>568</v>
+        <v>12</v>
       </c>
       <c r="F366" t="s">
         <v>12</v>
       </c>
       <c r="G366" s="5" t="s">
-        <v>568</v>
+        <v>12</v>
       </c>
       <c r="H366" t="s">
         <v>274</v>
@@ -11865,25 +11622,25 @@
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>569</v>
+        <v>505</v>
       </c>
       <c r="B367" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C367" t="s">
         <v>10</v>
       </c>
-      <c r="D367" t="s">
-        <v>12</v>
+      <c r="D367" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E367" s="5" t="s">
-        <v>12</v>
+        <v>506</v>
       </c>
       <c r="F367" t="s">
         <v>12</v>
       </c>
       <c r="G367" s="5" t="s">
-        <v>570</v>
+        <v>12</v>
       </c>
       <c r="H367" t="s">
         <v>274</v>
@@ -11891,25 +11648,25 @@
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>571</v>
+        <v>507</v>
       </c>
       <c r="B368" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C368" t="s">
-        <v>10</v>
-      </c>
-      <c r="D368" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D368" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E368" s="5" t="s">
-        <v>572</v>
+        <v>12</v>
       </c>
       <c r="F368" t="s">
         <v>12</v>
       </c>
       <c r="G368" s="5" t="s">
-        <v>572</v>
+        <v>12</v>
       </c>
       <c r="H368" t="s">
         <v>274</v>
@@ -11917,16 +11674,16 @@
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>573</v>
+        <v>508</v>
       </c>
       <c r="B369" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C369" t="s">
         <v>87</v>
       </c>
-      <c r="D369" t="s">
-        <v>12</v>
+      <c r="D369" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E369" s="5" t="s">
         <v>12</v>
@@ -11935,7 +11692,7 @@
         <v>12</v>
       </c>
       <c r="G369" s="5" t="s">
-        <v>574</v>
+        <v>12</v>
       </c>
       <c r="H369" t="s">
         <v>274</v>
@@ -11943,16 +11700,16 @@
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>575</v>
+        <v>509</v>
       </c>
       <c r="B370" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C370" t="s">
-        <v>395</v>
-      </c>
-      <c r="D370" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="D370" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E370" s="5" t="s">
         <v>12</v>
@@ -11961,7 +11718,7 @@
         <v>12</v>
       </c>
       <c r="G370" s="5" t="s">
-        <v>576</v>
+        <v>12</v>
       </c>
       <c r="H370" t="s">
         <v>274</v>
@@ -11969,16 +11726,16 @@
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>577</v>
+        <v>510</v>
       </c>
       <c r="B371" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C371" t="s">
         <v>10</v>
       </c>
-      <c r="D371" t="s">
-        <v>12</v>
+      <c r="D371" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E371" s="5" t="s">
         <v>12</v>
@@ -11987,7 +11744,7 @@
         <v>12</v>
       </c>
       <c r="G371" s="5" t="s">
-        <v>578</v>
+        <v>12</v>
       </c>
       <c r="H371" t="s">
         <v>274</v>
@@ -11995,16 +11752,16 @@
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>579</v>
+        <v>511</v>
       </c>
       <c r="B372" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C372" t="s">
         <v>87</v>
       </c>
-      <c r="D372" t="s">
-        <v>12</v>
+      <c r="D372" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E372" s="5" t="s">
         <v>12</v>
@@ -12013,7 +11770,7 @@
         <v>12</v>
       </c>
       <c r="G372" s="5" t="s">
-        <v>580</v>
+        <v>12</v>
       </c>
       <c r="H372" t="s">
         <v>274</v>
@@ -12021,16 +11778,16 @@
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>581</v>
+        <v>512</v>
       </c>
       <c r="B373" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C373" t="s">
         <v>10</v>
       </c>
-      <c r="D373" t="s">
-        <v>12</v>
+      <c r="D373" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E373" s="5" t="s">
         <v>12</v>
@@ -12039,7 +11796,7 @@
         <v>12</v>
       </c>
       <c r="G373" s="5" t="s">
-        <v>582</v>
+        <v>12</v>
       </c>
       <c r="H373" t="s">
         <v>274</v>
@@ -12047,16 +11804,16 @@
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>583</v>
+        <v>513</v>
       </c>
       <c r="B374" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C374" t="s">
-        <v>87</v>
-      </c>
-      <c r="D374" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D374" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E374" s="5" t="s">
         <v>12</v>
@@ -12065,7 +11822,7 @@
         <v>12</v>
       </c>
       <c r="G374" s="5" t="s">
-        <v>584</v>
+        <v>12</v>
       </c>
       <c r="H374" t="s">
         <v>274</v>
@@ -12073,16 +11830,16 @@
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>585</v>
+        <v>514</v>
       </c>
       <c r="B375" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C375" t="s">
-        <v>395</v>
-      </c>
-      <c r="D375" t="s">
-        <v>12</v>
+        <v>87</v>
+      </c>
+      <c r="D375" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E375" s="5" t="s">
         <v>12</v>
@@ -12091,7 +11848,7 @@
         <v>12</v>
       </c>
       <c r="G375" s="5" t="s">
-        <v>586</v>
+        <v>12</v>
       </c>
       <c r="H375" t="s">
         <v>274</v>
@@ -12099,16 +11856,16 @@
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>587</v>
+        <v>515</v>
       </c>
       <c r="B376" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C376" t="s">
-        <v>10</v>
-      </c>
-      <c r="D376" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="D376" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E376" s="5" t="s">
         <v>12</v>
@@ -12117,7 +11874,7 @@
         <v>12</v>
       </c>
       <c r="G376" s="5" t="s">
-        <v>588</v>
+        <v>12</v>
       </c>
       <c r="H376" t="s">
         <v>274</v>
@@ -12125,16 +11882,16 @@
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>589</v>
+        <v>516</v>
       </c>
       <c r="B377" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C377" t="s">
         <v>10</v>
       </c>
-      <c r="D377" t="s">
-        <v>12</v>
+      <c r="D377" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E377" s="5" t="s">
         <v>12</v>
@@ -12143,7 +11900,7 @@
         <v>12</v>
       </c>
       <c r="G377" s="5" t="s">
-        <v>475</v>
+        <v>12</v>
       </c>
       <c r="H377" t="s">
         <v>274</v>
@@ -12151,25 +11908,25 @@
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>590</v>
+        <v>517</v>
       </c>
       <c r="B378" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C378" t="s">
         <v>10</v>
       </c>
-      <c r="D378" t="s">
-        <v>12</v>
+      <c r="D378" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E378" s="5" t="s">
-        <v>591</v>
+        <v>12</v>
       </c>
       <c r="F378" t="s">
         <v>12</v>
       </c>
       <c r="G378" s="5" t="s">
-        <v>591</v>
+        <v>12</v>
       </c>
       <c r="H378" t="s">
         <v>274</v>
@@ -12177,16 +11934,16 @@
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>592</v>
+        <v>518</v>
       </c>
       <c r="B379" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C379" t="s">
-        <v>10</v>
-      </c>
-      <c r="D379" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D379" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E379" s="5" t="s">
         <v>12</v>
@@ -12195,7 +11952,7 @@
         <v>12</v>
       </c>
       <c r="G379" s="5" t="s">
-        <v>593</v>
+        <v>12</v>
       </c>
       <c r="H379" t="s">
         <v>274</v>
@@ -12203,25 +11960,25 @@
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>594</v>
+        <v>519</v>
       </c>
       <c r="B380" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C380" t="s">
         <v>10</v>
       </c>
-      <c r="D380" t="s">
-        <v>12</v>
+      <c r="D380" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E380" s="5" t="s">
-        <v>12</v>
+        <v>520</v>
       </c>
       <c r="F380" t="s">
         <v>12</v>
       </c>
       <c r="G380" s="5" t="s">
-        <v>595</v>
+        <v>12</v>
       </c>
       <c r="H380" t="s">
         <v>274</v>
@@ -12229,13 +11986,13 @@
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>596</v>
+        <v>521</v>
       </c>
       <c r="B381" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C381" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D381" s="6" t="s">
         <v>25</v>
@@ -12250,15 +12007,15 @@
         <v>12</v>
       </c>
       <c r="H381" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>597</v>
+        <v>522</v>
       </c>
       <c r="B382" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C382" t="s">
         <v>10</v>
@@ -12273,21 +12030,21 @@
         <v>12</v>
       </c>
       <c r="G382" s="5" t="s">
-        <v>598</v>
+        <v>12</v>
       </c>
       <c r="H382" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>599</v>
+        <v>523</v>
       </c>
       <c r="B383" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C383" t="s">
-        <v>395</v>
+        <v>24</v>
       </c>
       <c r="D383" s="6" t="s">
         <v>25</v>
@@ -12299,7 +12056,7 @@
         <v>12</v>
       </c>
       <c r="G383" s="5" t="s">
-        <v>600</v>
+        <v>524</v>
       </c>
       <c r="H383" t="s">
         <v>284</v>
@@ -12307,25 +12064,25 @@
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>601</v>
+        <v>525</v>
       </c>
       <c r="B384" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C384" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="D384" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E384" s="5" t="s">
-        <v>12</v>
+        <v>526</v>
       </c>
       <c r="F384" t="s">
         <v>12</v>
       </c>
       <c r="G384" s="5" t="s">
-        <v>602</v>
+        <v>12</v>
       </c>
       <c r="H384" t="s">
         <v>284</v>
@@ -12333,13 +12090,13 @@
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>603</v>
+        <v>527</v>
       </c>
       <c r="B385" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C385" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D385" s="6" t="s">
         <v>25</v>
@@ -12351,7 +12108,7 @@
         <v>12</v>
       </c>
       <c r="G385" s="5" t="s">
-        <v>604</v>
+        <v>12</v>
       </c>
       <c r="H385" t="s">
         <v>284</v>
@@ -12359,13 +12116,13 @@
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>605</v>
+        <v>528</v>
       </c>
       <c r="B386" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C386" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="D386" s="6" t="s">
         <v>25</v>
@@ -12377,7 +12134,7 @@
         <v>12</v>
       </c>
       <c r="G386" s="5" t="s">
-        <v>606</v>
+        <v>12</v>
       </c>
       <c r="H386" t="s">
         <v>284</v>
@@ -12385,16 +12142,16 @@
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>607</v>
+        <v>529</v>
       </c>
       <c r="B387" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C387" t="s">
-        <v>87</v>
-      </c>
-      <c r="D387" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D387" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E387" s="5" t="s">
         <v>12</v>
@@ -12403,7 +12160,7 @@
         <v>12</v>
       </c>
       <c r="G387" s="5" t="s">
-        <v>608</v>
+        <v>12</v>
       </c>
       <c r="H387" t="s">
         <v>284</v>
@@ -12411,16 +12168,16 @@
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>609</v>
+        <v>530</v>
       </c>
       <c r="B388" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C388" t="s">
-        <v>395</v>
-      </c>
-      <c r="D388" t="s">
-        <v>12</v>
+        <v>87</v>
+      </c>
+      <c r="D388" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E388" s="5" t="s">
         <v>12</v>
@@ -12429,7 +12186,7 @@
         <v>12</v>
       </c>
       <c r="G388" s="5" t="s">
-        <v>610</v>
+        <v>12</v>
       </c>
       <c r="H388" t="s">
         <v>284</v>
@@ -12437,16 +12194,16 @@
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>611</v>
+        <v>531</v>
       </c>
       <c r="B389" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C389" t="s">
-        <v>87</v>
-      </c>
-      <c r="D389" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="D389" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E389" s="5" t="s">
         <v>12</v>
@@ -12455,7 +12212,7 @@
         <v>12</v>
       </c>
       <c r="G389" s="5" t="s">
-        <v>612</v>
+        <v>12</v>
       </c>
       <c r="H389" t="s">
         <v>284</v>
@@ -12463,16 +12220,16 @@
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>613</v>
+        <v>532</v>
       </c>
       <c r="B390" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C390" t="s">
-        <v>87</v>
-      </c>
-      <c r="D390" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D390" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E390" s="5" t="s">
         <v>12</v>
@@ -12481,7 +12238,7 @@
         <v>12</v>
       </c>
       <c r="G390" s="5" t="s">
-        <v>614</v>
+        <v>12</v>
       </c>
       <c r="H390" t="s">
         <v>284</v>
@@ -12489,16 +12246,16 @@
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>615</v>
+        <v>533</v>
       </c>
       <c r="B391" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C391" t="s">
         <v>87</v>
       </c>
-      <c r="D391" t="s">
-        <v>12</v>
+      <c r="D391" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E391" s="5" t="s">
         <v>12</v>
@@ -12507,7 +12264,7 @@
         <v>12</v>
       </c>
       <c r="G391" s="5" t="s">
-        <v>616</v>
+        <v>12</v>
       </c>
       <c r="H391" t="s">
         <v>284</v>
@@ -12515,16 +12272,16 @@
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>195</v>
+        <v>534</v>
       </c>
       <c r="B392" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C392" t="s">
-        <v>24</v>
-      </c>
-      <c r="D392" t="s">
-        <v>12</v>
+        <v>87</v>
+      </c>
+      <c r="D392" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E392" s="5" t="s">
         <v>12</v>
@@ -12536,21 +12293,21 @@
         <v>12</v>
       </c>
       <c r="H392" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>617</v>
+        <v>535</v>
       </c>
       <c r="B393" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C393" t="s">
-        <v>395</v>
-      </c>
-      <c r="D393" s="4" t="s">
-        <v>11</v>
+        <v>87</v>
+      </c>
+      <c r="D393" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E393" s="5" t="s">
         <v>12</v>
@@ -12559,35 +12316,87 @@
         <v>12</v>
       </c>
       <c r="G393" s="5" t="s">
-        <v>618</v>
+        <v>12</v>
       </c>
       <c r="H393" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>619</v>
+        <v>536</v>
       </c>
       <c r="B394" s="12" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="C394" t="s">
+        <v>24</v>
+      </c>
+      <c r="D394" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E394" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F394" t="s">
+        <v>12</v>
+      </c>
+      <c r="G394" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H394" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A395" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B395" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="C395" t="s">
+        <v>64</v>
+      </c>
+      <c r="D395" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E395" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="F395" t="s">
+        <v>12</v>
+      </c>
+      <c r="G395" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H395" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A396" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B396" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="C396" t="s">
         <v>87</v>
       </c>
-      <c r="D394" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E394" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F394" t="s">
-        <v>12</v>
-      </c>
-      <c r="G394" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="H394" t="s">
+      <c r="D396" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E396" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F396" t="s">
+        <v>12</v>
+      </c>
+      <c r="G396" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H396" t="s">
         <v>294</v>
       </c>
     </row>
